--- a/data/b2_bonsucesso/B2 Bonsucesso 11-2025.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 11-2025.xlsx
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1017.68</v>
+        <v>1022.65</v>
       </c>
     </row>
     <row r="3">
@@ -4626,52 +4626,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1989.27</v>
+        <v>2307.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>65162.99</v>
+        <v>1625.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45970</v>
+        <v>45966</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2892.24</v>
+        <v>65494.09</v>
       </c>
     </row>
     <row r="6">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3539.3</v>
+        <v>3753.37</v>
       </c>
     </row>
     <row r="7">
@@ -4698,34 +4698,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>1227.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45973</v>
+        <v>45971</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2453.19</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1213.47</v>
+        <v>1296.45</v>
       </c>
     </row>
     <row r="10">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9373.18</v>
+        <v>10285.28</v>
       </c>
     </row>
     <row r="11">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1572.57</v>
+        <v>1676.16</v>
       </c>
     </row>
     <row r="12">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3776.39</v>
+        <v>3631.59</v>
       </c>
     </row>
     <row r="13">
@@ -4815,12 +4815,12 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>23056.81</v>
+        <v>22790.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -4829,11 +4829,11 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1644.22</v>
+        <v>1975.37</v>
       </c>
     </row>
     <row r="15">
@@ -4851,12 +4851,12 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3498.79</v>
+        <v>3887.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1354.16</v>
+        <v>1721.15</v>
       </c>
     </row>
     <row r="17">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3585.86</v>
+        <v>3402.18</v>
       </c>
     </row>
   </sheetData>
